--- a/data/trans_camb/P5B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,28</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,56</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -677,27 +677,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 7,8</t>
+          <t>-5,3; 8,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,92</t>
+          <t>-9,62; 0,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,9; -1,09</t>
+          <t>-11,15; -1,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 19,16</t>
+          <t>1,55; 16,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 15,21</t>
+          <t>2,6; 15,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 10,09</t>
+          <t>-0,5; 9,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 6,89</t>
+          <t>-1,09; 6,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,52</t>
+          <t>-4,82; -0,52</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>197,7%</t>
+          <t>200,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,75; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 1449,99</t>
+          <t>-59,57; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,91</t>
+          <t>7,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 6,41</t>
+          <t>-5,04; 8,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 4,75</t>
+          <t>-6,46; 4,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 56,72</t>
+          <t>-4,62; 60,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 9,89</t>
+          <t>-0,89; 10,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,86</t>
+          <t>-5,57; 1,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,0</t>
+          <t>-5,82; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 6,76</t>
+          <t>-1,71; 6,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,86</t>
+          <t>-4,13; 1,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 38,2</t>
+          <t>-3,3; 41,55</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>251,61%</t>
+          <t>252,57%</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,21; 428,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-83,83; 336,04</t>
+          <t>-85,95; 398,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,24 +1029,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,14; 412,64</t>
+          <t>-47,9; 413,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,68; 178,44</t>
+          <t>-82,18; 183,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-93,96; 3421,47</t>
+          <t>-92,18; 3986,21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 0,61</t>
+          <t>-10,3; 0,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,53; -2,27</t>
+          <t>-12,33; -2,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 1,44</t>
+          <t>-10,32; 0,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,06; -1,81</t>
+          <t>-10,11; -1,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,14; -1,81</t>
+          <t>-10,97; -1,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 2,51</t>
+          <t>-7,44; 2,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,99; -1,5</t>
+          <t>-7,85; -1,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -2,59</t>
+          <t>-8,57; -2,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 0,78</t>
+          <t>-6,78; 0,77</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 187,27</t>
+          <t>-100,0; 291,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 17,22</t>
+          <t>-100,0; 12,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-86,79; 52,94</t>
+          <t>-88,2; 43,48</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 6,6</t>
+          <t>-2,58; 7,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 8,82</t>
+          <t>-2,53; 8,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 0,0</t>
+          <t>-6,11; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -1,62</t>
+          <t>-9,26; -1,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,19</t>
+          <t>-7,11; 2,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 6,3</t>
+          <t>-4,8; 7,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 1,24</t>
+          <t>-4,55; 1,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 2,86</t>
+          <t>-3,99; 3,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 2,86</t>
+          <t>-3,92; 3,02</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-62,36%</t>
+          <t>-61,82%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-23,34%</t>
+          <t>-21,87%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 341,49</t>
+          <t>-81,37; 462,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 203,46</t>
+          <t>-100,0; 237,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 314,9</t>
+          <t>-100,0; 305,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-83,71; 288,12</t>
+          <t>-88,19; 261,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-49,07; 0,88</t>
+          <t>-48,19; 1,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -3,32</t>
+          <t>-50,35; -3,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-50,54; -7,09</t>
+          <t>-50,63; -7,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 13,53</t>
+          <t>-18,36; 13,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 3,39</t>
+          <t>-28,54; 3,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 2,31</t>
+          <t>-26,39; 2,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 4,75</t>
+          <t>-22,2; 4,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-27,59; -1,99</t>
+          <t>-28,23; -1,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-29,73; -2,74</t>
+          <t>-29,28; -2,76</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 169,04</t>
+          <t>-90,53; 166,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 9,35</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,54</t>
+          <t>0,0; 7,58</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-1,24</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-2,55</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>-2,44</t>
+          <t>-2,43</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-2,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 0,51</t>
+          <t>-6,59; 0,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 2,64</t>
+          <t>-5,42; 2,26</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 0,03</t>
+          <t>-7,13; -0,02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -1,21</t>
+          <t>-7,39; -0,77</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -1,2</t>
+          <t>-7,57; -0,82</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 0,39</t>
+          <t>-6,49; 0,84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,91; -1,03</t>
+          <t>-5,92; -1,06</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,06; -0,26</t>
+          <t>-5,17; -0,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,35; -0,76</t>
+          <t>-5,23; -0,57</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-31,79%</t>
+          <t>-31,42%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-61,61%</t>
+          <t>-61,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-60,46%</t>
+          <t>-60,35%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-66,95%</t>
+          <t>-66,83%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 177,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-84,05; 214,49</t>
+          <t>-87,06; 148,14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,54</t>
+          <t>-100,0; 96,61</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 9,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-100,0; 8,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-93,56; 49,24</t>
+          <t>-100,0; 71,56</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -17,22</t>
+          <t>-100,0; -19,61</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-87,9; 4,58</t>
+          <t>-88,19; 1,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-91,58; -10,15</t>
+          <t>-90,39; -5,9</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>-3,16</t>
+          <t>-3,15</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,5; -0,09</t>
+          <t>-8,0; -0,25</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,64; -0,13</t>
+          <t>-7,33; -0,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,88; -1,23</t>
+          <t>-8,14; -1,39</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,74; -1,2</t>
+          <t>-7,15; -0,71</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -1,2</t>
+          <t>-7,25; -0,88</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 0,34</t>
+          <t>-6,13; 0,44</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -1,13</t>
+          <t>-5,54; -1,23</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -1,34</t>
+          <t>-5,98; -1,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -0,84</t>
+          <t>-5,56; -1,04</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-82,02%</t>
+          <t>-81,9%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>-91,0%</t>
+          <t>-90,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-84,95%</t>
+          <t>-84,91%</t>
         </is>
       </c>
     </row>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 164,37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,67</t>
+          <t>-100,0; -6,53</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -10,71</t>
+          <t>-100,0; -51,47</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -11,44</t>
+          <t>-100,0; -20,76</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-2,04</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,53</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,12</t>
+          <t>-3,47; -0,09</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,43</t>
+          <t>-3,73; -0,54</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 14,71</t>
+          <t>-3,65; 12,78</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,01</t>
+          <t>-2,95; -0,1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,54</t>
+          <t>-3,24; -0,59</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,15; -0,42</t>
+          <t>-3,22; -0,36</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,65</t>
+          <t>-2,87; -0,58</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,95</t>
+          <t>-3,13; -0,97</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,83</t>
+          <t>-2,72; 5,66</t>
         </is>
       </c>
     </row>
@@ -2458,47 +2458,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-47,24%</t>
+          <t>-47,1%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-53,49%</t>
+          <t>-53,28%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-48,55%</t>
+          <t>-48,41%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-63,38%</t>
+          <t>-63,33%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-57,55%</t>
+          <t>-57,46%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>-48,08%</t>
+          <t>-47,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>-58,14%</t>
+          <t>-58,02%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-15,78%</t>
+          <t>-15,64%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-73,01; -0,95</t>
+          <t>-72,84; -1,56</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-77,0; -14,11</t>
+          <t>-75,13; -14,4</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-87,54; 464,95</t>
+          <t>-87,6; 498,65</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-75,32; 4,31</t>
+          <t>-75,89; -0,24</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-83,44; -16,93</t>
+          <t>-82,83; -22,11</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-79,09; -16,51</t>
+          <t>-79,43; -11,62</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-69,89; -21,84</t>
+          <t>-70,72; -19,61</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-74,46; -31,68</t>
+          <t>-75,54; -33,51</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-75,79; 194,8</t>
+          <t>-76,23; 183,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Provincia-trans_camb.xlsx
@@ -677,27 +677,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 8,79</t>
+          <t>-6,26; 8,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 0,89</t>
+          <t>-8,51; 1,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,15; -1,1</t>
+          <t>-9,93; -1,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 16,07</t>
+          <t>1,61; 18,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 15,9</t>
+          <t>2,48; 15,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 9,96</t>
+          <t>-0,61; 10,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 6,49</t>
+          <t>-0,9; 7,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; -0,52</t>
+          <t>-4,98; -0,53</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,57; 1560,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,57; —</t>
+          <t>-65,39; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 8,15</t>
+          <t>-6,19; 7,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 4,78</t>
+          <t>-6,39; 5,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 60,3</t>
+          <t>-4,56; 58,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 10,0</t>
+          <t>-0,7; 10,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 1,52</t>
+          <t>-4,92; 1,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,0</t>
+          <t>-6,02; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 6,54</t>
+          <t>-1,58; 6,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,97</t>
+          <t>-4,26; 2,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 41,55</t>
+          <t>-3,44; 37,77</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,49; 444,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,95; 398,31</t>
+          <t>-85,13; 329,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,9; 413,25</t>
+          <t>-45,96; 424,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,18; 183,18</t>
+          <t>-82,66; 172,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-92,18; 3986,21</t>
+          <t>-94,29; 2684,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 0,97</t>
+          <t>-9,99; 1,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -2,12</t>
+          <t>-11,99; -2,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 0,99</t>
+          <t>-9,31; 1,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,11; -1,81</t>
+          <t>-9,21; -1,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,97; -1,8</t>
+          <t>-10,12; -1,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 2,88</t>
+          <t>-6,68; 2,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; -1,36</t>
+          <t>-8,33; -1,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,57; -2,51</t>
+          <t>-9,34; -2,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 0,77</t>
+          <t>-7,46; 0,66</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 291,71</t>
+          <t>-90,45; 297,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 12,98</t>
+          <t>-100,0; 50,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-88,2; 43,48</t>
+          <t>-88,79; 39,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 7,63</t>
+          <t>-2,57; 7,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 8,25</t>
+          <t>-2,33; 8,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,0</t>
+          <t>-5,28; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,26; -1,63</t>
+          <t>-9,51; -1,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 2,62</t>
+          <t>-6,93; 2,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 7,24</t>
+          <t>-5,22; 7,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,59</t>
+          <t>-4,55; 1,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,14</t>
+          <t>-3,69; 3,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 3,02</t>
+          <t>-3,97; 2,65</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,37; 462,57</t>
+          <t>-87,26; 398,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 237,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 305,66</t>
+          <t>-100,0; 264,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 261,76</t>
+          <t>-89,2; 211,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-48,19; 1,16</t>
+          <t>-44,16; 0,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-50,35; -3,36</t>
+          <t>-48,85; -3,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-50,63; -7,16</t>
+          <t>-50,73; -7,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 13,67</t>
+          <t>-18,68; 12,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,54; 3,36</t>
+          <t>-25,21; 2,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 2,27</t>
+          <t>-24,06; 2,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 4,62</t>
+          <t>-25,37; 4,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-28,23; -1,51</t>
+          <t>-28,05; -1,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-29,28; -2,76</t>
+          <t>-27,17; -2,74</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-90,53; 166,9</t>
+          <t>-100,0; 154,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,35</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>0,0; 6,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 0,45</t>
+          <t>-6,78; 0,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 2,26</t>
+          <t>-5,44; 2,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,13; -0,02</t>
+          <t>-7,08; -0,31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -0,77</t>
+          <t>-7,26; -0,69</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,57; -0,82</t>
+          <t>-7,8; -1,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,84</t>
+          <t>-6,57; 0,52</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,92; -1,06</t>
+          <t>-6,13; -0,95</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,17; -0,18</t>
+          <t>-5,28; -0,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,57</t>
+          <t>-5,51; -0,49</t>
         </is>
       </c>
     </row>
@@ -2084,42 +2084,42 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-87,06; 148,14</t>
+          <t>-85,55; 189,6</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,61</t>
+          <t>-100,0; 56,9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 86,67</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 8,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 71,56</t>
+          <t>-93,88; 60,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,61</t>
+          <t>-94,94; -1,22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 1,31</t>
+          <t>-87,61; 0,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-90,39; -5,9</t>
+          <t>-91,3; 0,99</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,0; -0,25</t>
+          <t>-7,04; -0,07</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,33; -0,59</t>
+          <t>-7,38; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,14; -1,39</t>
+          <t>-7,89; -1,22</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -0,71</t>
+          <t>-7,74; -1,21</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,25; -0,88</t>
+          <t>-7,91; -1,22</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 0,44</t>
+          <t>-6,77; 0,25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,54; -1,23</t>
+          <t>-5,73; -1,23</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,98; -1,39</t>
+          <t>-5,85; -1,34</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,56; -1,04</t>
+          <t>-5,53; -1,02</t>
         </is>
       </c>
     </row>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 164,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -6,53</t>
+          <t>-100,0; -27,24</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -51,47</t>
+          <t>-100,0; -37,16</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -20,76</t>
+          <t>-100,0; -12,98</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,09</t>
+          <t>-3,46; -0,18</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,54</t>
+          <t>-3,57; -0,4</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 12,78</t>
+          <t>-3,54; 14,19</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,1</t>
+          <t>-2,91; -0,17</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,59</t>
+          <t>-3,21; -0,59</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,36</t>
+          <t>-3,05; -0,37</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,87; -0,58</t>
+          <t>-2,78; -0,54</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,13; -0,97</t>
+          <t>-3,04; -0,89</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,66</t>
+          <t>-2,78; 7,16</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-72,84; -1,56</t>
+          <t>-74,47; -4,28</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-75,13; -14,4</t>
+          <t>-73,98; -10,43</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-87,6; 498,65</t>
+          <t>-86,94; 425,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-75,89; -0,24</t>
+          <t>-75,69; 2,51</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-82,83; -22,11</t>
+          <t>-83,15; -20,15</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-79,43; -11,62</t>
+          <t>-77,36; -13,2</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-70,72; -19,61</t>
+          <t>-68,26; -14,79</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-75,54; -33,51</t>
+          <t>-73,63; -29,8</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-76,23; 183,81</t>
+          <t>-75,77; 263,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,94</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-3,73</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,94</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 8,03</t>
+          <t>1,6; 19,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 1,04</t>
+          <t>2,66; 15,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 18,68</t>
+          <t>-5,39; 8,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 15,25</t>
+          <t>-8,87; 0,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,9; -1,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 10,31</t>
+          <t>-0,47; 10,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 7,12</t>
+          <t>-1,12; 6,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; -0,53</t>
+          <t>-4,88; -0,52</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>7,5%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-72,32%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,57; 1560,63</t>
+          <t>-74,88; inf</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,39; —</t>
+          <t>-63,94; 1449,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,69</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,05</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,89</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,72</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,19</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17,76</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,69</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,89</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>-1,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 7,42</t>
+          <t>-0,73; 9,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 5,02</t>
+          <t>-5,51; 0,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 58,9</t>
+          <t>-6,26; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 10,56</t>
+          <t>-5,09; 6,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 1,48</t>
+          <t>-6,05; 4,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 0,0</t>
+          <t>-5,87; 9,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 6,74</t>
+          <t>-1,74; 6,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 2,08</t>
+          <t>-4,22; 1,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 37,77</t>
+          <t>-4,46; 3,17</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>195,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-55,62%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-4,44%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>408,31%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>195,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-55,62%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-6,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>252,57%</t>
+          <t>-39,39%</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-84,49; 444,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,13; 329,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-81,21; 428,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,83; 336,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 424,55</t>
+          <t>-52,14; 412,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,66; 172,4</t>
+          <t>-81,68; 178,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-94,29; 2684,17</t>
+          <t>-96,95; 498,99</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,59</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,59</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-4,14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-5,63</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,58</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,59</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,59</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>-3,65</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-2,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 1,14</t>
+          <t>-10,06; -1,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,99; -2,1</t>
+          <t>-10,14; -1,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 1,78</t>
+          <t>-7,55; 2,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,21; -1,83</t>
+          <t>-10,14; 0,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,12; -1,8</t>
+          <t>-12,5; -2,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,88</t>
+          <t>-10,19; 1,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,33; -1,42</t>
+          <t>-7,99; -1,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,34; -2,52</t>
+          <t>-9,1; -2,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 0,66</t>
+          <t>-6,66; 0,65</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-43,7%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-73,49%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-63,68%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-64,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-86,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-42,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-86,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-53,54%</t>
+          <t>-55,07%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 180,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 297,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,3</t>
+          <t>-100,0; 17,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-88,79; 39,13</t>
+          <t>-87,09; 45,49</t>
         </is>
       </c>
     </row>
@@ -1272,34 +1272,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-4,26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,63</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,48</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-1,73</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-4,26</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,63</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>-1,7</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,66</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 7,6</t>
+          <t>-9,19; -1,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 8,69</t>
+          <t>-6,88; 3,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,0</t>
+          <t>-5,22; 6,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,51; -1,62</t>
+          <t>-2,59; 6,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 2,43</t>
+          <t>-2,46; 8,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 7,04</t>
+          <t>-6,1; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,18</t>
+          <t>-4,63; 1,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 3,61</t>
+          <t>-3,66; 3,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 2,65</t>
+          <t>-3,58; 3,07</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-61,82%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>66,6%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>85,58%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-61,82%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>-55,54%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-23,2%</t>
+          <t>-21,54%</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 367,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,26; 398,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 203,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 264,7</t>
+          <t>-100,0; 296,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-89,2; 211,7</t>
+          <t>-83,39; 305,78</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,9</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-4,46</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,96</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-17,85</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-20,05</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-21,99</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-4,46</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-4,99</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 0,97</t>
+          <t>-16,01; 13,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-48,85; -3,3</t>
+          <t>-29,5; 3,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-50,73; -7,09</t>
+          <t>-24,85; 2,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 12,94</t>
+          <t>-49,07; 0,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 2,49</t>
+          <t>-46,55; -3,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 2,39</t>
+          <t>-50,54; -7,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 4,39</t>
+          <t>-23,86; 4,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-28,05; -1,6</t>
+          <t>-27,59; -1,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-27,17; -2,74</t>
+          <t>-29,73; -2,73</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>30,8%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-72,21%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-80,21%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-81,19%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-91,17%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>30,8%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-72,21%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-80,71%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>-52,06%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-95,18%</t>
+          <t>-95,19%</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 154,96</t>
+          <t>-100,0; 169,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>1,63</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,65</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-3,6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-3,61</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-2,47</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-2,69</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-1,23</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-2,91</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-3,6</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-3,61</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,55</t>
+          <t>-2,79</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-2,61</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 0,17</t>
+          <t>-7,81; -1,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 2,24</t>
+          <t>-7,76; -1,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -0,31</t>
+          <t>-6,19; 0,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,26; -0,69</t>
+          <t>-6,62; 0,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -1,07</t>
+          <t>-5,39; 2,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 0,52</t>
+          <t>-6,63; 0,21</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,13; -0,95</t>
+          <t>-5,91; -1,03</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,24</t>
+          <t>-5,39; -0,32</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,51; -0,49</t>
+          <t>-5,36; -0,4</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-86,72%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-86,95%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-59,48%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-68,84%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-31,42%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-74,31%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-86,72%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-86,95%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-61,37%</t>
+          <t>-71,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-66,83%</t>
+          <t>-64,77%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 9,71</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-85,55; 189,6</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,9</t>
+          <t>-94,13; 126,37</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 86,67</t>
+          <t>-100,0; 177,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,07; 167,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-93,88; 60,21</t>
+          <t>-100,0; 74,71</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-94,94; -1,22</t>
+          <t>-100,0; -17,22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-87,61; 0,6</t>
+          <t>-88,64; 15,29</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-91,3; 0,99</t>
+          <t>-90,54; 4,0</t>
         </is>
       </c>
     </row>
@@ -2136,34 +2136,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-3,26</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-3,26</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-2,35</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-3,03</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-3,09</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>-3,7</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-3,26</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-3,26</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-2,3</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>-3,15</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-2,98</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,04; -0,07</t>
+          <t>-7,45; -1,19</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 0,0</t>
+          <t>-7,51; -1,2</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -1,22</t>
+          <t>-6,63; 0,29</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,74; -1,21</t>
+          <t>-7,85; -0,07</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,91; -1,22</t>
+          <t>-7,64; -0,13</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,25</t>
+          <t>-8,1; -1,25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -1,23</t>
+          <t>-5,87; -1,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -1,34</t>
+          <t>-5,73; -1,34</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -1,02</t>
+          <t>-5,55; -1,06</t>
         </is>
       </c>
     </row>
@@ -2242,34 +2242,34 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-72,12%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-81,9%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-83,48%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-70,51%</t>
-        </is>
-      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
           <t>-90,92%</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-84,91%</t>
+          <t>-86,04%</t>
         </is>
       </c>
     </row>
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -27,24</t>
+          <t>-100,0; -34,69</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -37,16</t>
+          <t>-100,0; -10,71</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -12,98</t>
+          <t>-100,0; -12,13</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-1,69</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-1,8</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-2,04</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-2,17</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -0,18</t>
+          <t>-3,08; 0,03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,4</t>
+          <t>-3,36; -0,73</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 14,19</t>
+          <t>-3,19; -0,33</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,91; -0,17</t>
+          <t>-3,67; -0,05</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,59</t>
+          <t>-3,75; -0,44</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,05; -0,37</t>
+          <t>-4,25; -0,88</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -0,54</t>
+          <t>-2,77; -0,53</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,89</t>
+          <t>-3,07; -1,01</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 7,16</t>
+          <t>-3,27; -1,13</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-48,41%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-63,33%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-56,03%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-47,1%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-53,28%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-48,41%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-63,33%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-57,46%</t>
+          <t>-69,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-15,64%</t>
+          <t>-63,56%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-74,47; -4,28</t>
+          <t>-76,73; 2,66</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-73,98; -10,43</t>
+          <t>-83,75; -24,98</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-86,94; 425,01</t>
+          <t>-79,71; -9,03</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-75,69; 2,51</t>
+          <t>-73,27; 4,52</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-83,15; -20,15</t>
+          <t>-75,39; -9,33</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-77,36; -13,2</t>
+          <t>-87,72; -19,45</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-68,26; -14,79</t>
+          <t>-67,48; -17,53</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-73,63; -29,8</t>
+          <t>-75,65; -31,37</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-75,77; 263,92</t>
+          <t>-79,2; -37,13</t>
         </is>
       </c>
     </row>
